--- a/output_qg/01_normal_pass/reports/fraud_report.xlsx
+++ b/output_qg/01_normal_pass/reports/fraud_report.xlsx
@@ -464,7 +464,7 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46183.00369352902</v>
+        <v>46183.0097973805</v>
       </c>
     </row>
     <row r="3">
